--- a/sheets/조재수대금교본/검수/El condor pasa.xlsx
+++ b/sheets/조재수대금교본/검수/El condor pasa.xlsx
@@ -3772,14 +3772,14 @@
       <c r="P3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">太
-黃?</t>
+黃</t>
         </is>
       </c>
       <c r="Q3" s="24"/>
       <c r="R3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林仲
-–ﾉ</t>
+–</t>
         </is>
       </c>
       <c r="S3" s="22"/>
@@ -3830,11 +3830,7 @@
     </row>
     <row r="5" ht="106.4" customHeight="true">
       <c r="A5" s="0"/>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B5" s="21"/>
       <c r="C5" s="28"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
@@ -3864,7 +3860,6 @@
       <c r="N5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-‹
 南南</t>
         </is>
       </c>
@@ -3885,7 +3880,7 @@
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲ﾉ</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="C6" s="22"/>
@@ -3938,17 +3933,12 @@
         </is>
       </c>
       <c r="Q6" s="22"/>
-      <c r="R6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R6" s="21"/>
       <c r="S6" s="22"/>
       <c r="T6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㴌
-‹</t>
+㴌</t>
         </is>
       </c>
       <c r="U6" s="22"/>
@@ -3975,7 +3965,7 @@
       <c r="G7" s="27"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰ㄱ</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="I7" s="27"/>
@@ -3989,7 +3979,7 @@
       <c r="L7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–潢?</t>
+–潢</t>
         </is>
       </c>
       <c r="M7" s="30"/>
@@ -4008,7 +3998,7 @@
       <c r="Q7" s="27"/>
       <c r="R7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃ﾉ</t>
+          <t xml:space="preserve">黃</t>
         </is>
       </c>
       <c r="S7" s="27"/>
@@ -4030,8 +4020,7 @@
       <c r="G8" s="28"/>
       <c r="H8" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">ʒ
-–ㄱ</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I8" s="29"/>
@@ -4056,7 +4045,7 @@
       <c r="S8" s="28"/>
       <c r="T8" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ
+          <t xml:space="preserve">潢
 –</t>
         </is>
       </c>
@@ -4083,14 +4072,13 @@
       <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–ㄱ</t>
+–</t>
         </is>
       </c>
       <c r="I9" s="22"/>
       <c r="J9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-‹
 湳湳</t>
         </is>
       </c>
@@ -4102,11 +4090,7 @@
         </is>
       </c>
       <c r="M9" s="22"/>
-      <c r="N9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N9" s="21"/>
       <c r="O9" s="22"/>
       <c r="P9" s="21"/>
       <c r="Q9" s="22"/>
@@ -4134,8 +4118,7 @@
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太仲
-林南
-‹</t>
+林南</t>
         </is>
       </c>
       <c r="G10" s="27"/>
@@ -4162,7 +4145,7 @@
       <c r="M10" s="27"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲ﾉ</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="O10" s="27"/>
@@ -4180,11 +4163,7 @@
         </is>
       </c>
       <c r="S10" s="27"/>
-      <c r="T10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T10" s="21"/>
       <c r="U10" s="27"/>
     </row>
     <row r="11" ht="106.4" customHeight="true">
@@ -4199,7 +4178,7 @@
       <c r="E11" s="28"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰ㄱ</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="G11" s="28"/>
@@ -4296,35 +4275,22 @@
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–ㄱ</t>
+–</t>
         </is>
       </c>
       <c r="G13" s="27"/>
       <c r="H13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-‹
 汰汰</t>
         </is>
       </c>
       <c r="I13" s="31"/>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J13" s="21"/>
       <c r="K13" s="27"/>
-      <c r="L13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L13" s="21"/>
       <c r="M13" s="27"/>
-      <c r="N13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N13" s="21"/>
       <c r="O13" s="27"/>
       <c r="P13" s="21" t="inlineStr">
         <is>
@@ -4365,13 +4331,13 @@
       <c r="I14" s="28"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱﾉ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="K14" s="28"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ﾉ</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="M14" s="28"/>
@@ -4393,7 +4359,6 @@
       <c r="T14" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-‹
 南</t>
         </is>
       </c>

--- a/sheets/조재수대금교본/검수/El condor pasa.xlsx
+++ b/sheets/조재수대금교본/검수/El condor pasa.xlsx
@@ -3779,7 +3779,7 @@
       <c r="R3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林仲
-–</t>
+–ﾉ</t>
         </is>
       </c>
       <c r="S3" s="22"/>
@@ -3880,7 +3880,7 @@
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">仲ﾉ</t>
         </is>
       </c>
       <c r="C6" s="22"/>
@@ -3965,7 +3965,7 @@
       <c r="G7" s="27"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰ㄱ</t>
         </is>
       </c>
       <c r="I7" s="27"/>
@@ -3998,7 +3998,7 @@
       <c r="Q7" s="27"/>
       <c r="R7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃</t>
+          <t xml:space="preserve">黃ﾉ</t>
         </is>
       </c>
       <c r="S7" s="27"/>
@@ -4020,7 +4020,8 @@
       <c r="G8" s="28"/>
       <c r="H8" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">ʒ
+–ㄱ</t>
         </is>
       </c>
       <c r="I8" s="29"/>
@@ -4045,7 +4046,7 @@
       <c r="S8" s="28"/>
       <c r="T8" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">潢ʒ
 –</t>
         </is>
       </c>
@@ -4072,7 +4073,7 @@
       <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–</t>
+–ㄱ</t>
         </is>
       </c>
       <c r="I9" s="22"/>
@@ -4145,7 +4146,7 @@
       <c r="M10" s="27"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">仲ﾉ</t>
         </is>
       </c>
       <c r="O10" s="27"/>
@@ -4178,7 +4179,7 @@
       <c r="E11" s="28"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰ㄱ</t>
         </is>
       </c>
       <c r="G11" s="28"/>
@@ -4275,7 +4276,7 @@
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–</t>
+–ㄱ</t>
         </is>
       </c>
       <c r="G13" s="27"/>
@@ -4331,13 +4332,13 @@
       <c r="I14" s="28"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱﾉ</t>
         </is>
       </c>
       <c r="K14" s="28"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢ﾉ</t>
         </is>
       </c>
       <c r="M14" s="28"/>

--- a/sheets/조재수대금교본/검수/El condor pasa.xlsx
+++ b/sheets/조재수대금교본/검수/El condor pasa.xlsx
@@ -3671,32 +3671,32 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13.46" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="13.46" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="13.46" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="13.46" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="13.46" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="13.46" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="71.43" customHeight="true">
+    <row r="2" ht="93.02" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="106.4" customHeight="true">
+    <row r="3" ht="138.71" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="U3" s="26"/>
     </row>
-    <row r="4" ht="106.4" customHeight="true">
+    <row r="4" ht="138.71" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="27"/>
@@ -3828,7 +3828,7 @@
       <c r="T4" s="21"/>
       <c r="U4" s="27"/>
     </row>
-    <row r="5" ht="106.4" customHeight="true">
+    <row r="5" ht="138.71" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="28"/>
@@ -3876,7 +3876,7 @@
       <c r="T5" s="21"/>
       <c r="U5" s="28"/>
     </row>
-    <row r="6" ht="106.4" customHeight="true">
+    <row r="6" ht="138.71" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="U6" s="22"/>
     </row>
-    <row r="7" ht="106.4" customHeight="true">
+    <row r="7" ht="138.71" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="U7" s="27"/>
     </row>
-    <row r="8" ht="106.4" customHeight="true">
+    <row r="8" ht="138.71" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="28"/>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="U8" s="29"/>
     </row>
-    <row r="9" ht="106.4" customHeight="true">
+    <row r="9" ht="138.71" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -4100,7 +4100,7 @@
       <c r="T9" s="21"/>
       <c r="U9" s="22"/>
     </row>
-    <row r="10" ht="106.4" customHeight="true">
+    <row r="10" ht="138.71" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
       <c r="T10" s="21"/>
       <c r="U10" s="27"/>
     </row>
-    <row r="11" ht="106.4" customHeight="true">
+    <row r="11" ht="138.71" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="28"/>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="U11" s="28"/>
     </row>
-    <row r="12" ht="106.4" customHeight="true">
+    <row r="12" ht="138.71" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="U12" s="22"/>
     </row>
-    <row r="13" ht="106.4" customHeight="true">
+    <row r="13" ht="138.71" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="27"/>
@@ -4305,7 +4305,7 @@
       <c r="T13" s="21"/>
       <c r="U13" s="27"/>
     </row>
-    <row r="14" ht="106.4" customHeight="true">
+    <row r="14" ht="138.71" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="28"/>
@@ -4371,6 +4371,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="56"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="43"/>
 </worksheet>
 </file>